--- a/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
@@ -175,22 +175,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -734,7 +734,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-01  ·  Generated 2026-06-04T18:47:58  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-01  ·  Generated 2026-06-10T09:47:02  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1001797.36</v>
+        <v>1004898.62</v>
       </c>
     </row>
     <row r="5">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3.643</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="6">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.999</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="7">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2.672</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="8">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="10">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>43.23</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.187</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="12">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.8081</v>
+        <v>0.8213</v>
       </c>
     </row>
     <row r="13">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -846,7 +846,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>6.16 / 3.08</t>
+          <t>6.74 / 3.37</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>3.643</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="16">
@@ -868,7 +868,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>MS (37.03% NAV)</t>
+          <t>MS (36.91% NAV)</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>43.23</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="7">
@@ -1049,7 +1049,7 @@
       <c r="B13" s="13" t="n">
         <v>5858.42</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>13.06</v>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       <c r="B15" s="13" t="n">
         <v>3838.46</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>8.550000000000001</v>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       <c r="B17" s="13" t="n">
         <v>2481.21</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>5.53</v>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       <c r="B19" s="13" t="n">
         <v>1931.05</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       <c r="B21" s="13" t="n">
         <v>1813.36</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>4.04</v>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       <c r="B23" s="13" t="n">
         <v>1450.71</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>3.23</v>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       <c r="B25" s="13" t="n">
         <v>1025.02</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>2.28</v>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>CI/MTD</t>
         </is>
@@ -1325,7 +1325,7 @@
       <c r="D7" s="13" t="n">
         <v>1732535</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
           <t>MS</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>MS/AWK</t>
         </is>
@@ -1367,7 +1367,7 @@
       <c r="D9" s="13" t="n">
         <v>5339471</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
           <t>MKTX</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>ODFL/MKTX</t>
         </is>
@@ -1409,7 +1409,7 @@
       <c r="D11" s="13" t="n">
         <v>634158</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
           <t>JKHY</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>ODFL/JKHY</t>
         </is>
@@ -1451,7 +1451,7 @@
       <c r="D13" s="13" t="n">
         <v>1396873</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1482,18 +1482,18 @@
           <t>REGN</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="15" t="n">
         <v>23</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>1056976</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
           <t>IQV</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>PANW/IQV</t>
         </is>
@@ -1535,7 +1535,7 @@
       <c r="D17" s="13" t="n">
         <v>1886644</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>KLAC/LOW</t>
         </is>
@@ -1577,7 +1577,7 @@
       <c r="D19" s="13" t="n">
         <v>3091973</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1654,11 +1654,11 @@
           <t>SPY -5%</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
-        <v>-133840.13</v>
+      <c r="B4" s="19" t="n">
+        <v>-133852.5</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>-13.36</v>
+        <v>-13.32</v>
       </c>
     </row>
     <row r="5">
@@ -1667,11 +1667,11 @@
           <t>SPY -10%</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
-        <v>-267680.25</v>
+      <c r="B5" s="18" t="n">
+        <v>-267704.99</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>-26.72</v>
+        <v>-26.64</v>
       </c>
     </row>
     <row r="6">
@@ -1680,11 +1680,11 @@
           <t>VIX +10pt</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
-        <v>-133840.13</v>
+      <c r="B6" s="19" t="n">
+        <v>-133852.5</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>-13.36</v>
+        <v>-13.32</v>
       </c>
     </row>
     <row r="7">
@@ -1693,11 +1693,11 @@
           <t>Top sector -10%</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="18" t="n">
         <v>-87020.66</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>-8.69</v>
+        <v>-8.66</v>
       </c>
     </row>
   </sheetData>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C4" s="32" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="D4" s="32" t="n">
         <v>3</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="C6" s="34" t="n">
-        <v>7.55</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="D6" s="34" t="n">
         <v>3</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="C7" s="34" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="D7" s="34" t="n">
         <v>0.5</v>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="C8" s="34" t="n">
-        <v>37.03</v>
+        <v>36.91</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>15</v>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="C9" s="34" t="n">
-        <v>33.47</v>
+        <v>33.36</v>
       </c>
       <c r="D9" s="34" t="n">
         <v>15</v>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>32.36</v>
+        <v>32.26</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>15</v>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="D13" s="34" t="n">
         <v>0.3</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="D14" s="36" t="n">
         <v>3</v>
@@ -2192,17 +2192,17 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>CI/MTD</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>short</t>
         </is>
@@ -2213,18 +2213,18 @@
       <c r="F4" s="13" t="n">
         <v>274.19</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="18" t="n">
         <v>-85547.28</v>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="I4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="I4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>vol_agnostic</t>
         </is>
@@ -2280,17 +2280,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>MS/AWK</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2304,15 +2304,15 @@
       <c r="G6" s="13" t="n">
         <v>370955.58</v>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="I6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="I6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -2345,7 +2345,7 @@
       <c r="F7" s="4" t="n">
         <v>121.13</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="19" t="n">
         <v>-324143.88</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -2368,17 +2368,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>ODFL/MKTX</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>ODFL</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2392,15 +2392,15 @@
       <c r="G8" s="13" t="n">
         <v>59874.86</v>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="I8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>sensitive_reversal</t>
         </is>
@@ -2433,7 +2433,7 @@
       <c r="F9" s="4" t="n">
         <v>129.29</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="19" t="n">
         <v>-51198.84</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -2456,17 +2456,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>ODFL/JKHY</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>ODFL</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2480,15 +2480,15 @@
       <c r="G10" s="13" t="n">
         <v>29251.84</v>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="I10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>conservative</t>
         </is>
@@ -2521,7 +2521,7 @@
       <c r="F11" s="4" t="n">
         <v>140.2</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="19" t="n">
         <v>-26778.2</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -2544,17 +2544,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>KLAC</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2568,15 +2568,15 @@
       <c r="G12" s="13" t="n">
         <v>129982.68</v>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="I12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>beta_neutral_long_term</t>
         </is>
@@ -2609,7 +2609,7 @@
       <c r="F13" s="4" t="n">
         <v>600.66</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>-13815.18</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -2632,17 +2632,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>PANW/IQV</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>PANW</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2656,15 +2656,15 @@
       <c r="G14" s="13" t="n">
         <v>70011.84</v>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="I14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>monthly_aligned_windows</t>
         </is>
@@ -2697,7 +2697,7 @@
       <c r="F15" s="4" t="n">
         <v>186.82</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>-65387</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -2720,17 +2720,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>KLAC/LOW</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>KLAC</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2744,15 +2744,15 @@
       <c r="G16" s="13" t="n">
         <v>81481.67999999999</v>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="I16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
@@ -2785,7 +2785,7 @@
       <c r="F17" s="4" t="n">
         <v>207.7</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>-79341.39999999999</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2808,17 +2808,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>FFIV/VLTO</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>FFIV</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2832,15 +2832,15 @@
       <c r="G18" s="13" t="n">
         <v>168534.12</v>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="I18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>long_term_tilt</t>
         </is>
@@ -2873,7 +2873,7 @@
       <c r="F19" s="11" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="19" t="n">
         <v>-55594</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2896,17 +2896,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>LRCX/BSX</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>LRCX</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2920,15 +2920,15 @@
       <c r="G20" s="13" t="n">
         <v>136678.72</v>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="I20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
@@ -2961,7 +2961,7 @@
       <c r="F21" s="11" t="n">
         <v>47.98</v>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="19" t="n">
         <v>-81853.88</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2984,17 +2984,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>LRCX/RMD</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>LRCX</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3008,15 +3008,15 @@
       <c r="G22" s="13" t="n">
         <v>136678.72</v>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="I22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>fast_rebalance</t>
         </is>
@@ -3049,7 +3049,7 @@
       <c r="F23" s="4" t="n">
         <v>186.44</v>
       </c>
-      <c r="G23" s="18" t="n">
+      <c r="G23" s="19" t="n">
         <v>-53694.72</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -3072,17 +3072,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>ORCL/LOW</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3096,15 +3096,15 @@
       <c r="G24" s="13" t="n">
         <v>60300.45</v>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="I24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>fast_strict</t>
         </is>
@@ -3137,7 +3137,7 @@
       <c r="F25" s="4" t="n">
         <v>207.7</v>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="19" t="n">
         <v>-53171.2</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -3160,17 +3160,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>CSCO/CAG</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>CSCO</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3184,15 +3184,15 @@
       <c r="G26" s="13" t="n">
         <v>110652.96</v>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="I26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
         <is>
           <t>fast_strict</t>
         </is>
@@ -3225,7 +3225,7 @@
       <c r="F27" s="11" t="n">
         <v>13.11</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="19" t="n">
         <v>-54236.07</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -3248,17 +3248,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>NUE/INTU</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>NUE</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3272,15 +3272,15 @@
       <c r="G28" s="13" t="n">
         <v>82740.21000000001</v>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="I28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>conservative</t>
         </is>
@@ -3313,7 +3313,7 @@
       <c r="F29" s="4" t="n">
         <v>353.76</v>
       </c>
-      <c r="G29" s="18" t="n">
+      <c r="G29" s="19" t="n">
         <v>-29008.32</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -3336,17 +3336,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>CSCO/REGN</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>CSCO</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3360,15 +3360,15 @@
       <c r="G30" s="13" t="n">
         <v>110652.96</v>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="I30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>monthly_aligned_windows</t>
         </is>
@@ -3401,7 +3401,7 @@
       <c r="F31" s="4" t="n">
         <v>600.66</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G31" s="19" t="n">
         <v>-53458.74</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -3424,17 +3424,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>NUE/MKTX</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>NUE</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3448,15 +3448,15 @@
       <c r="G32" s="13" t="n">
         <v>82740.21000000001</v>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="I32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -3489,7 +3489,7 @@
       <c r="F33" s="4" t="n">
         <v>129.29</v>
       </c>
-      <c r="G33" s="18" t="n">
+      <c r="G33" s="19" t="n">
         <v>-54560.38</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3512,17 +3512,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>STLD/ISRG</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>STLD</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3536,15 +3536,15 @@
       <c r="G34" s="13" t="n">
         <v>131318.18</v>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="I34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t>beta_neutral</t>
         </is>
@@ -3577,7 +3577,7 @@
       <c r="F35" s="4" t="n">
         <v>412.26</v>
       </c>
-      <c r="G35" s="18" t="n">
+      <c r="G35" s="19" t="n">
         <v>-32568.54</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -3600,17 +3600,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>BWA/VLTO</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>BWA</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3618,21 +3618,21 @@
       <c r="E36" s="28" t="n">
         <v>2359</v>
       </c>
-      <c r="F36" s="17" t="n">
+      <c r="F36" s="15" t="n">
         <v>71.06</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>167630.54</v>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="I36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
@@ -3665,7 +3665,7 @@
       <c r="F37" s="11" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="G37" s="18" t="n">
+      <c r="G37" s="19" t="n">
         <v>-80339.60000000001</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -3688,17 +3688,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>STLD/HII</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>STLD</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3712,15 +3712,15 @@
       <c r="G38" s="13" t="n">
         <v>131318.18</v>
       </c>
-      <c r="H38" s="16" t="inlineStr">
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="I38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -3753,7 +3753,7 @@
       <c r="F39" s="4" t="n">
         <v>296.41</v>
       </c>
-      <c r="G39" s="18" t="n">
+      <c r="G39" s="19" t="n">
         <v>-52760.98</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -3776,17 +3776,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>BWA/CME</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>BWA</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3794,21 +3794,21 @@
       <c r="E40" s="28" t="n">
         <v>2359</v>
       </c>
-      <c r="F40" s="17" t="n">
+      <c r="F40" s="15" t="n">
         <v>71.06</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>167630.54</v>
       </c>
-      <c r="H40" s="16" t="inlineStr">
+      <c r="H40" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="I40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
@@ -3841,7 +3841,7 @@
       <c r="F41" s="4" t="n">
         <v>257.76</v>
       </c>
-      <c r="G41" s="18" t="n">
+      <c r="G41" s="19" t="n">
         <v>-76812.48</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -3934,7 +3934,7 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>CI/MTD</t>
         </is>
@@ -3945,15 +3945,15 @@
       <c r="D4" s="13" t="n">
         <v>182600.02</v>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>vol_agnostic</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>short</t>
         </is>
@@ -3996,7 +3996,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>ODFL/MKTX</t>
         </is>
@@ -4007,15 +4007,15 @@
       <c r="D6" s="13" t="n">
         <v>111073.7</v>
       </c>
-      <c r="E6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>sensitive_reversal</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4058,26 +4058,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="18" t="n">
         <v>-3999.37</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>143797.86</v>
       </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>beta_neutral_long_term</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4120,7 +4120,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>KLAC/LOW</t>
         </is>
@@ -4131,15 +4131,15 @@
       <c r="D10" s="13" t="n">
         <v>160823.08</v>
       </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4182,7 +4182,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>LRCX/BSX</t>
         </is>
@@ -4193,15 +4193,15 @@
       <c r="D12" s="13" t="n">
         <v>218532.6</v>
       </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4244,7 +4244,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>ORCL/LOW</t>
         </is>
@@ -4255,15 +4255,15 @@
       <c r="D14" s="13" t="n">
         <v>113471.65</v>
       </c>
-      <c r="E14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>fast_strict</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4306,26 +4306,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>NUE/INTU</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="18" t="n">
         <v>-1332.65</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>111748.53</v>
       </c>
-      <c r="E16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>conservative</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4368,7 +4368,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>NUE/MKTX</t>
         </is>
@@ -4379,15 +4379,15 @@
       <c r="D18" s="13" t="n">
         <v>137300.59</v>
       </c>
-      <c r="E18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4430,26 +4430,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>BWA/VLTO</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="18" t="n">
         <v>-2708.38</v>
       </c>
       <c r="D20" s="13" t="n">
         <v>247970.14</v>
       </c>
-      <c r="E20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4492,7 +4492,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>BWA/CME</t>
         </is>
@@ -4503,15 +4503,15 @@
       <c r="D22" s="13" t="n">
         <v>244443.02</v>
       </c>
-      <c r="E22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="E22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4586,12 +4586,12 @@
           <t>T_1D</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -4620,12 +4620,12 @@
           <t>T_1M</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>15.74</v>
+        <v>14.9</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-0.58</v>
+        <v>-0.6</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>-16.32</v>
+        <v>-15.5</v>
       </c>
     </row>
     <row r="7">
@@ -4728,17 +4728,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="D7" s="16" t="n">
+      <c r="B7" s="17" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>-4.64</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="8">
@@ -4748,16 +4748,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>29.09</v>
+        <v>24.67</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>7.42</v>
+        <v>3.74</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-21.67</v>
+        <v>-20.93</v>
       </c>
     </row>
     <row r="9">
@@ -4766,17 +4766,17 @@
           <t>AISS</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>41.85</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="D9" s="16" t="n">
+      <c r="B9" s="17" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>42.63</v>
+        <v>44.23</v>
       </c>
     </row>
     <row r="11">
@@ -4814,7 +4814,7 @@
           <t>LRCX/BSX</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>13.06</v>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>8.550000000000001</v>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
           <t>STLD/ISRG</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>5.53</v>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
           <t>NUE/MKTX</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
           <t>ODFL/MKTX</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>4.04</v>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
           <t>NUE/INTU</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>3.23</v>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
           <t>BWA/CME</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>2.28</v>
       </c>
     </row>
@@ -5056,30 +5056,30 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>38.26</v>
+        <v>38.97</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>0.006 (t=0.07)</t>
+          <t>0.003 (t=0.04)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>-0.082 (t=-0.61)</t>
+          <t>-0.075 (t=-0.55)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>0.081 (t=0.67)</t>
+          <t>0.073 (t=0.6)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.101 (t=-0.57)</t>
+          <t>-0.111 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>-0.108 (t=-1.71)</t>
+          <t>-0.11 (t=-1.72)</t>
         </is>
       </c>
     </row>
@@ -5105,45 +5105,45 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>36.87</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E6" s="16" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="E6" s="17" t="n">
         <v>116</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>0.151 (t=0.82)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>-0.231 (t=-0.81)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>-0.027 (t=-0.11)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>0.33 (t=1.39)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>-0.246 (t=-0.66)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>-0.163 (t=-1.22)</t>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>0.056 (t=0.39)</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>-0.116 (t=-0.52)</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>-0.06 (t=-0.31)</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>0.241 (t=1.31)</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>-0.207 (t=-0.72)</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>-0.141 (t=-1.36)</t>
         </is>
       </c>
     </row>
@@ -5154,45 +5154,45 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>44.08</v>
+        <v>28.62</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.026</v>
+        <v>0.036</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.2 (t=-0.81)</t>
+          <t>-0.069 (t=-0.42)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>0.156 (t=0.41)</t>
+          <t>-0.004 (t=-0.02)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.19 (t=0.56)</t>
+          <t>0.235 (t=1.04)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.225 (t=-0.71)</t>
+          <t>-0.103 (t=-0.49)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.076 (t=0.15)</t>
+          <t>0.022 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.035 (t=-0.19)</t>
+          <t>-0.065 (t=-0.55)</t>
         </is>
       </c>
     </row>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>-0.592</v>
+        <v>-0.523</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>4.745</v>
+        <v>3.81</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -5293,10 +5293,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1.29</v>
+        <v>1.259</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1.344</v>
+        <v>1.313</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0.054</v>
@@ -5308,26 +5308,26 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>-2.969</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>21.188</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="16" t="b">
+      <c r="B5" s="17" t="n">
+        <v>-0.416</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>2.037</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>2.356</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>0.319</v>
+      <c r="F5" s="17" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3.412</v>
+        <v>0.165</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>32.679</v>
+        <v>12.035</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -5349,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3.09</v>
+        <v>2.513</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>3.09</v>
+        <v>2.513</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -5417,31 +5417,31 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.187</v>
+        <v>1.252</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.8081</v>
+        <v>0.8213</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>511</v>
+        <v>458</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8.640000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>9.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>77.2</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>6.16</v>
+        <v>6.74</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>3.08</v>
+        <v>3.37</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.643</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="10">
@@ -5450,32 +5450,32 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>0.6783</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>1807</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>0.336</v>
+      <c r="B10" s="17" t="n">
+        <v>1.437</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0.8551</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>346</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>0.316</v>
       </c>
     </row>
     <row r="11">
@@ -5485,13 +5485,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0.761</v>
+        <v>0.368</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.7323</v>
+        <v>0.6092</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1009</v>
+        <v>5035</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.04</v>
@@ -5503,13 +5503,13 @@
         <v>80.7</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.95</v>
+        <v>0.67</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.97</v>
+        <v>0.33</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>7.552</v>
+        <v>8.127000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>170601.51</v>
+        <v>155329.01</v>
       </c>
     </row>
     <row r="6">
@@ -5650,7 +5650,7 @@
         <v>3443683.26</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>2135705.7</v>
+        <v>2120433.21</v>
       </c>
     </row>
     <row r="9">
@@ -5675,452 +5675,452 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
+          <t>Margin Loan 保证金借款</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>26485.41</v>
+        <v>1347073.8</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>19000.22</v>
+        <v>564075.33</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>30716.47</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>21341.93</v>
+        <v>910972.4300000001</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1323689.65</v>
+        <v>2671344.49</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>548953.54</v>
+        <v>1514086.47</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>883533.92</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>2446795.81</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>1067096.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>2674445.75</v>
+        <v>1004898.62</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1517964.9</v>
+        <v>989347.35</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>2450073.77</v>
+        <v>996887.45</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1088438.31</v>
+        <v>1053336.82</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>1001797.36</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>985468.92</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>993609.49</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1047267.39</v>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>3.632</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>3.424</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>1.845</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>3.643</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>2.521</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>3.435</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>1.856</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>-0.182</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>729951.54</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>496886.72</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>682593.36</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>388752.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
+          <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>729951.54</v>
+        <v>274947.08</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>496886.72</v>
+        <v>492460.63</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>682593.36</v>
+        <v>314294.09</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>388752.45</v>
+        <v>664584.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>271845.82</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>488582.2</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>311016.13</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>658514.9399999999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>COMBINED — 双账户法</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1004898.62</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>989347.35</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>996887.45</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>876665.88</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>2325487.01</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1534422.46</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1877143.41</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>876665.88</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>1320588.39</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>545075.11</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>880255.96</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1004898.62</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>989347.35</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>996887.45</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>876665.88</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>21341.93</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>21341.93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>1324270.69</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>950011.14</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>1535823.38</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>1067096.39</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>1324270.69</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>950011.14</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>1535823.38</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>1067096.39</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>26485.41</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>19000.22</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>30716.47</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Short Book — NAV</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>21341.93</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Unallocated Cash 未分配现金</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
         <v>-0</v>
       </c>
-      <c r="C18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>COMBINED — 双账户法</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>638307.24</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>608639.99</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>546488.62</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>472333.27</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>2325487.01</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1534422.46</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1877143.41</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>876665.88</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="n">
-        <v>1687179.77</v>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>925782.47</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>1330654.79</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>404332.61</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>638307.24</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>608639.99</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>546488.62</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>472333.27</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n">
-        <v>363490.12</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>376828.93</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>447120.87</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>574934.12</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>363490.12</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>376828.93</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>447120.87</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>574934.12</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n">
-        <v>1324270.69</v>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>950011.14</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>1535823.38</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>1067096.39</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>1324270.69</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>950011.14</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1535823.38</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>1067096.39</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Short Book — NAV</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="n">
-        <v>363490.12</v>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>376828.93</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>447120.87</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>574934.12</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Unallocated Cash 未分配现金</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>0</v>
+      <c r="C32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>155329.01</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
-        <v>1001797.36</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>985468.92</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>993609.49</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>1047267.39</v>
+      <c r="B33" s="4" t="n">
+        <v>1004898.62</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>989347.35</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>996887.45</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1053336.82</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
+      <c r="B34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6165,16 +6165,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>445650.55</v>
+        <v>479492.41</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>387907.1</v>
+        <v>420303.88</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>222453.92</v>
+        <v>249710.29</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>391791.5</v>
+        <v>426377.54</v>
       </c>
     </row>
     <row r="40">
@@ -6222,16 +6222,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>629961.52</v>
+        <v>663803.38</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>691644.21</v>
+        <v>724040.99</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>953006.89</v>
+        <v>980263.26</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>789058.45</v>
+        <v>823644.49</v>
       </c>
     </row>
     <row r="43">
@@ -6256,452 +6256,452 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="n">
-        <v>1710.95</v>
-      </c>
-      <c r="C44" s="13" t="n">
-        <v>2974.69</v>
-      </c>
-      <c r="D44" s="13" t="n">
-        <v>8103.05</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <v>3940.45</v>
+          <t>Margin Loan 保证金借款</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>0</v>
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>85547.28</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>148734.48</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>405152.69</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>197022.47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>87258.23</v>
+        <v>578256.1</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>151709.17</v>
+        <v>575306.51</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>413255.74</v>
+        <v>575110.5699999999</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>200962.92</v>
+        <v>626622.02</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>542703.29</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>539935.04</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>539751.15</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>588095.53</v>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>0.628</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>1.338</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.669</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>-0.153</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-0.001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>-0.163</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>-0.001</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>36520</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>60152.48</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>144489.98</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>78665.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
+          <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>36520</v>
+        <v>541736.1</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>60152.48</v>
+        <v>515154.03</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>144489.98</v>
+        <v>430620.59</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>78665.3</v>
+        <v>547956.72</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>506183.29</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>479782.56</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>395261.17</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>509430.23</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0</v>
+      <c r="B51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>MRPT — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>MRPT — 双账户法</t>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>97052.74000000001</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>152027.94</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>317297.23</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>196304.03</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>288449.26</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>272923.76</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>237056.63</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>293510.66</v>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="n">
-        <v>191396.52</v>
-      </c>
-      <c r="C57" s="13" t="n">
-        <v>120895.82</v>
-      </c>
-      <c r="D57" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="13" t="n">
-        <v>97206.63</v>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>97052.74000000001</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>152027.94</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>317297.23</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>196304.03</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
         <v>97052.74000000001</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C59" s="4" t="n">
         <v>152027.94</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D59" s="4" t="n">
         <v>317297.23</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E59" s="4" t="n">
         <v>196304.03</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="13" t="n">
-        <v>80240.60000000001</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>288449.26</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>272923.76</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>237056.63</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>293510.66</v>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n">
+        <v>1710.95</v>
+      </c>
+      <c r="C60" s="13" t="n">
+        <v>2974.69</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>8103.05</v>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>3940.45</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="n">
-        <v>254254.03</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>267011.28</v>
-      </c>
-      <c r="D61" s="13" t="n">
-        <v>302694.52</v>
-      </c>
-      <c r="E61" s="13" t="n">
-        <v>294584.87</v>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>1710.95</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>2974.69</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>8103.05</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>3940.45</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>254254.03</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>267011.28</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>302694.52</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>294584.87</v>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>85547.28</v>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>148734.48</v>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>405152.69</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>197022.47</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="n">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
         <v>85547.28</v>
       </c>
-      <c r="C63" s="13" t="n">
+      <c r="C63" s="4" t="n">
         <v>148734.48</v>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="4" t="n">
         <v>405152.69</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="4" t="n">
         <v>197022.47</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>85547.28</v>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>148734.48</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>405152.69</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>197022.47</v>
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B65" s="13" t="n">
-        <v>254254.03</v>
-      </c>
-      <c r="C65" s="13" t="n">
-        <v>267011.28</v>
-      </c>
-      <c r="D65" s="13" t="n">
-        <v>302694.52</v>
-      </c>
-      <c r="E65" s="13" t="n">
-        <v>294584.87</v>
+      <c r="B65" s="4" t="n">
+        <v>1710.95</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>2974.69</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>8103.05</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>3940.45</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E66" s="11" t="n">
-        <v>0</v>
+      <c r="B66" s="13" t="n">
+        <v>479492.41</v>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>420303.88</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>249710.29</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>426377.54</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B67" s="13" t="n">
-        <v>542703.29</v>
-      </c>
-      <c r="C67" s="13" t="n">
-        <v>539935.04</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>539751.15</v>
-      </c>
-      <c r="E67" s="13" t="n">
-        <v>588095.53</v>
+      <c r="B67" s="4" t="n">
+        <v>578256.1</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>575306.51</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>575110.5699999999</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>626622.02</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="7" t="n">
+      <c r="B68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6837,452 +6837,452 @@
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
+          <t>Margin Loan 保证金借款</t>
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>24774.47</v>
+        <v>1826566.22</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>16025.53</v>
+        <v>984379.21</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>22613.41</v>
+        <v>1160682.71</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>17401.48</v>
+        <v>271048.54</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1769340.19</v>
+        <v>3065289.63</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>936860.64</v>
+        <v>1785655.87</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1105987.84</v>
+        <v>2291353.4</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>221190.01</v>
+        <v>1141122.45</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>3032838.07</v>
+        <v>426642.52</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>1754162.83</v>
+        <v>414040.84</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>2259271.94</v>
+        <v>421776.88</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>1108665.4</v>
+        <v>426714.8</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="n">
-        <v>459094.08</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>445533.88</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>453858.34</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>459171.85</v>
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>8.127000000000001</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>5.274</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>6.379</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>3.633</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B82" s="16" t="n">
-        <v>7.552</v>
-      </c>
-      <c r="C82" s="16" t="n">
-        <v>4.901</v>
-      </c>
-      <c r="D82" s="16" t="n">
-        <v>5.928</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>3.377</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="C82" s="17" t="n">
+        <v>1.404</v>
+      </c>
+      <c r="D82" s="17" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>-0.445</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="n">
-        <v>2.156</v>
-      </c>
-      <c r="C83" s="7" t="n">
-        <v>1.304</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="E83" s="7" t="n">
-        <v>-0.413</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n">
+        <v>693431.54</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>436734.24</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>538103.37</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>310087.15</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>693431.54</v>
-      </c>
-      <c r="C84" s="13" t="n">
-        <v>436734.24</v>
-      </c>
-      <c r="D84" s="13" t="n">
-        <v>538103.37</v>
+          <t>Excess Liquidity 超额流动性</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="n">
+        <v>-266789.02</v>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>-22693.4</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>-116326.49</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>310087.15</v>
+        <v>116627.65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B85" s="18" t="n">
-        <v>-234337.46</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>8799.639999999999</v>
-      </c>
-      <c r="D85" s="18" t="n">
-        <v>-84245.03</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>149084.7</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="16" t="n">
+      <c r="B85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="E86" s="16" t="n">
-        <v>0</v>
+      <c r="E85" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>MTFS — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>MTFS — 双账户法</t>
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="n">
+        <v>426642.52</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>414040.84</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>421776.88</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>426714.8</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>295071.95</v>
-      </c>
-      <c r="C90" s="4" t="n">
-        <v>282049.61</v>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>263127.58</v>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>201493.68</v>
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0</v>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>2228434.27</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>1382394.52</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>1559846.18</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>680361.86</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>2228434.27</v>
-      </c>
-      <c r="C92" s="4" t="n">
-        <v>1382394.52</v>
-      </c>
-      <c r="D92" s="4" t="n">
-        <v>1559846.18</v>
-      </c>
-      <c r="E92" s="4" t="n">
-        <v>680361.86</v>
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="n">
+        <v>1801791.75</v>
+      </c>
+      <c r="C92" s="13" t="n">
+        <v>968353.6800000001</v>
+      </c>
+      <c r="D92" s="13" t="n">
+        <v>1138069.3</v>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>253647.06</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="n">
-        <v>1933362.32</v>
-      </c>
-      <c r="C93" s="13" t="n">
-        <v>1100344.91</v>
-      </c>
-      <c r="D93" s="13" t="n">
-        <v>1296718.6</v>
-      </c>
-      <c r="E93" s="13" t="n">
-        <v>478868.18</v>
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n">
+        <v>426642.52</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>414040.84</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>421776.88</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>426714.8</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="n">
-        <v>295071.95</v>
-      </c>
-      <c r="C94" s="4" t="n">
-        <v>282049.61</v>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>263127.58</v>
-      </c>
-      <c r="E94" s="4" t="n">
-        <v>201493.68</v>
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="n">
-        <v>164022.13</v>
-      </c>
-      <c r="C95" s="13" t="n">
-        <v>163484.27</v>
-      </c>
-      <c r="D95" s="13" t="n">
-        <v>190730.76</v>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>257678.17</v>
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="n">
-        <v>164022.13</v>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>163484.27</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>190730.76</v>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>257678.17</v>
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="n">
+        <v>1238723.41</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>801276.66</v>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>1130670.69</v>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>870073.91</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="n">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n">
         <v>1238723.41</v>
       </c>
-      <c r="C97" s="13" t="n">
+      <c r="C97" s="4" t="n">
         <v>801276.66</v>
       </c>
-      <c r="D97" s="13" t="n">
+      <c r="D97" s="4" t="n">
         <v>1130670.69</v>
       </c>
-      <c r="E97" s="13" t="n">
+      <c r="E97" s="4" t="n">
         <v>870073.91</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="n">
-        <v>1238723.41</v>
-      </c>
-      <c r="C98" s="4" t="n">
-        <v>801276.66</v>
-      </c>
-      <c r="D98" s="4" t="n">
-        <v>1130670.69</v>
-      </c>
-      <c r="E98" s="4" t="n">
-        <v>870073.91</v>
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>24774.47</v>
+      </c>
+      <c r="C98" s="13" t="n">
+        <v>16025.53</v>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>22613.41</v>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>17401.48</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B99" s="13" t="n">
-        <v>164022.13</v>
-      </c>
-      <c r="C99" s="13" t="n">
-        <v>163484.27</v>
-      </c>
-      <c r="D99" s="13" t="n">
-        <v>190730.76</v>
-      </c>
-      <c r="E99" s="13" t="n">
-        <v>257678.17</v>
+      <c r="B99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B100" s="11" t="n">
+      <c r="B100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="15" t="n">
         <v>-0</v>
       </c>
-      <c r="C100" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="11" t="n">
+      <c r="D100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="14" t="inlineStr">
+      <c r="A101" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B101" s="13" t="n">
-        <v>459094.08</v>
-      </c>
-      <c r="C101" s="13" t="n">
-        <v>445533.88</v>
-      </c>
-      <c r="D101" s="13" t="n">
-        <v>453858.34</v>
-      </c>
-      <c r="E101" s="13" t="n">
-        <v>459171.85</v>
+      <c r="B101" s="4" t="n">
+        <v>426642.52</v>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>414040.84</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>421776.88</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>426714.8</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="7" t="n">
+      <c r="B102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7352,22 +7352,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16328.44</v>
+        <v>15551.27</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>8187.87</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>-45470.03</v>
+        <v>8011.17</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>-48438.2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>80298.57000000001</v>
+        <v>83399.83</v>
       </c>
     </row>
     <row r="6">
@@ -7377,16 +7377,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>181.33</v>
+        <v>184.53</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>906.64</v>
+        <v>922.65</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>3807.87</v>
+        <v>3875.14</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>26292.47</v>
+        <v>26756.95</v>
       </c>
     </row>
     <row r="7">
@@ -7434,22 +7434,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2768.25</v>
+        <v>2949.59</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2952.14</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>-45392.24</v>
+        <v>3145.53</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>-48365.92</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>33371.35</v>
+        <v>68924.16</v>
       </c>
     </row>
     <row r="12">
@@ -7458,16 +7458,16 @@
           <t>Interest expense (est)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17" t="n">
+      <c r="B12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7516,22 +7516,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>13560.2</v>
+        <v>12601.68</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5235.74</v>
-      </c>
-      <c r="D17" s="19" t="n">
-        <v>-77.77</v>
+        <v>4865.64</v>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>-72.28</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>46927.23</v>
+        <v>14475.67</v>
       </c>
     </row>
     <row r="18">
@@ -7541,16 +7541,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>242.38</v>
+        <v>250.21</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1211.88</v>
+        <v>1251.07</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>5089.88</v>
+        <v>5254.51</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>35144.43</v>
+        <v>36281.11</v>
       </c>
     </row>
     <row r="19">
@@ -7636,19 +7636,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>985468.92</v>
+        <v>989347.35</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>993609.49</v>
+        <v>996887.45</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1047267.39</v>
+        <v>1053336.82</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -7661,16 +7661,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>16328.44</v>
+        <v>15551.27</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>8187.87</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>-45470.03</v>
+        <v>8011.17</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>-48438.2</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>80298.57000000001</v>
+        <v>83399.83</v>
       </c>
     </row>
     <row r="7">
@@ -7698,36 +7698,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="17" t="n">
+      <c r="B8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1001797.36</v>
+        <v>1004898.62</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1001797.36</v>
+        <v>1004898.62</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1001797.36</v>
+        <v>1004898.62</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1001797.36</v>
+        <v>1004898.62</v>
       </c>
     </row>
     <row r="10">
@@ -7737,16 +7737,16 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>-4.34</v>
+        <v>-4.6</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>8.710000000000001</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -7759,13 +7759,13 @@
         <v>0</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>-2.97</v>
+        <v>-2.68</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-5.9</v>
+        <v>-6.07</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-9.57</v>
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -7803,19 +7803,19 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>539935.04</v>
+        <v>575306.51</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>539751.15</v>
+        <v>575110.5699999999</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>588095.53</v>
+        <v>626622.02</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -7828,16 +7828,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>2768.25</v>
+        <v>2949.59</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>2952.14</v>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>-45392.24</v>
+        <v>3145.53</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>-48365.92</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>33371.35</v>
+        <v>68924.16</v>
       </c>
     </row>
     <row r="17">
@@ -7865,36 +7865,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="17" t="n">
+      <c r="B18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>542703.29</v>
+        <v>578256.1</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>542703.29</v>
+        <v>578256.1</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>542703.29</v>
+        <v>578256.1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>542703.29</v>
+        <v>578256.1</v>
       </c>
     </row>
     <row r="20">
@@ -7913,7 +7913,7 @@
         <v>-7.72</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>6.55</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="21">
@@ -7932,7 +7932,7 @@
         <v>-9.550000000000001</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>-11.77</v>
+        <v>-9.550000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -7970,19 +7970,19 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>445533.88</v>
+        <v>414040.84</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>453858.34</v>
+        <v>421776.88</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>459171.85</v>
+        <v>426714.8</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -7995,16 +7995,16 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>13560.2</v>
+        <v>12601.68</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>5235.74</v>
+        <v>4865.64</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>-77.77</v>
+        <v>-72.28</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>46927.23</v>
+        <v>14475.67</v>
       </c>
     </row>
     <row r="27">
@@ -8032,36 +8032,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="17" t="n">
+      <c r="B28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>459094.08</v>
+        <v>426642.52</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>459094.08</v>
+        <v>426642.52</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>459094.08</v>
+        <v>426642.52</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>459094.08</v>
+        <v>426642.52</v>
       </c>
     </row>
     <row r="30">
@@ -8080,7 +8080,7 @@
         <v>-0.02</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>11.39</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="31">
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>8187.87</v>
+        <v>8011.17</v>
       </c>
     </row>
     <row r="5">
@@ -8158,7 +8158,7 @@
           <t>Investing cash flow</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="19" t="n">
         <v>-659896.29</v>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>440155.73</v>
+        <v>436101.37</v>
       </c>
     </row>
     <row r="7">
@@ -8178,8 +8178,8 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
-        <v>-211552.69</v>
+      <c r="B7" s="19" t="n">
+        <v>-215783.75</v>
       </c>
     </row>
     <row r="8">
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1010661.06</v>
+        <v>1011218.51</v>
       </c>
     </row>
     <row r="97">
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1023679.41</v>
+        <v>1025407</v>
       </c>
     </row>
     <row r="98">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1025724.19</v>
+        <v>1026941.31</v>
       </c>
     </row>
     <row r="99">
@@ -9206,7 +9206,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015750.02</v>
+        <v>1015258.85</v>
       </c>
     </row>
     <row r="100">
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003777.26</v>
+        <v>1003003.03</v>
       </c>
     </row>
     <row r="101">
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1014086.2</v>
+        <v>1013068.4</v>
       </c>
     </row>
     <row r="102">
@@ -9236,7 +9236,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1028383.17</v>
+        <v>1026667.89</v>
       </c>
     </row>
     <row r="103">
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1057042.21</v>
+        <v>1053397.75</v>
       </c>
     </row>
     <row r="104">
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1054438.15</v>
+        <v>1050736.08</v>
       </c>
     </row>
     <row r="105">
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1052315.58</v>
+        <v>1049499.07</v>
       </c>
     </row>
     <row r="106">
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1051354.61</v>
+        <v>1049134.93</v>
       </c>
     </row>
     <row r="107">
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1044479.78</v>
+        <v>1042919.9</v>
       </c>
     </row>
     <row r="108">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1050335.11</v>
+        <v>1048685.92</v>
       </c>
     </row>
     <row r="109">
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1044442.91</v>
+        <v>1042773.4</v>
       </c>
     </row>
     <row r="110">
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1046176.28</v>
+        <v>1044235.83</v>
       </c>
     </row>
     <row r="111">
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1072213.58</v>
+        <v>1070354.14</v>
       </c>
     </row>
     <row r="112">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1063030.61</v>
+        <v>1061514.84</v>
       </c>
     </row>
     <row r="113">
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1075175.58</v>
+        <v>1074870.62</v>
       </c>
     </row>
     <row r="114">
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080207.25</v>
+        <v>1080512.52</v>
       </c>
     </row>
     <row r="115">
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1085910.78</v>
+        <v>1086924.48</v>
       </c>
     </row>
     <row r="116">
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1072326.04</v>
+        <v>1071780.32</v>
       </c>
     </row>
     <row r="117">
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065410.49</v>
+        <v>1065526.09</v>
       </c>
     </row>
     <row r="118">
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1079552.28</v>
+        <v>1080594.32</v>
       </c>
     </row>
     <row r="119">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1073850.36</v>
+        <v>1075591.99</v>
       </c>
     </row>
     <row r="120">
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1068923.8</v>
+        <v>1071013.67</v>
       </c>
     </row>
     <row r="121">
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1071061.15</v>
+        <v>1073689.47</v>
       </c>
     </row>
     <row r="122">
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1071649.93</v>
+        <v>1074236.64</v>
       </c>
     </row>
     <row r="123">
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1081609.49</v>
+        <v>1084547.15</v>
       </c>
     </row>
     <row r="124">
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1082665.34</v>
+        <v>1085528.37</v>
       </c>
     </row>
     <row r="125">
@@ -9466,7 +9466,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1089743.49</v>
+        <v>1092616.33</v>
       </c>
     </row>
     <row r="126">
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1089711.86</v>
+        <v>1092781.06</v>
       </c>
     </row>
     <row r="127">
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1047267.39</v>
+        <v>1053336.82</v>
       </c>
     </row>
     <row r="128">
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1043747.85</v>
+        <v>1049687.33</v>
       </c>
     </row>
     <row r="129">
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1038522.14</v>
+        <v>1044100.12</v>
       </c>
     </row>
     <row r="130">
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1027387.75</v>
+        <v>1032626.83</v>
       </c>
     </row>
     <row r="131">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1034795.94</v>
+        <v>1039700.39</v>
       </c>
     </row>
     <row r="132">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1032907.49</v>
+        <v>1037551.62</v>
       </c>
     </row>
     <row r="133">
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1015331.02</v>
+        <v>1019311.74</v>
       </c>
     </row>
     <row r="134">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1010937.91</v>
+        <v>1014163.76</v>
       </c>
     </row>
     <row r="135">
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>996866.8</v>
+        <v>999293.04</v>
       </c>
     </row>
     <row r="136">
@@ -9576,7 +9576,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1008057.17</v>
+        <v>1011409.78</v>
       </c>
     </row>
     <row r="137">
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1010905.61</v>
+        <v>1014540.8</v>
       </c>
     </row>
     <row r="138">
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1008270.67</v>
+        <v>1011881.11</v>
       </c>
     </row>
     <row r="139">
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>995181.03</v>
+        <v>998415.39</v>
       </c>
     </row>
     <row r="140">
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1012313.28</v>
+        <v>1014351.76</v>
       </c>
     </row>
     <row r="141">
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1021177.12</v>
+        <v>1023498.77</v>
       </c>
     </row>
     <row r="142">
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1022017.19</v>
+        <v>1023696.66</v>
       </c>
     </row>
     <row r="143">
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>993609.49</v>
+        <v>996887.45</v>
       </c>
     </row>
     <row r="144">
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1015610.69</v>
+        <v>1016573.57</v>
       </c>
     </row>
     <row r="145">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>995802</v>
+        <v>997861.24</v>
       </c>
     </row>
     <row r="146">
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>988320.51</v>
+        <v>991493.7</v>
       </c>
     </row>
     <row r="147">
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>985468.92</v>
+        <v>989347.35</v>
       </c>
     </row>
     <row r="148">
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1001797.36</v>
+        <v>1004898.62</v>
       </c>
     </row>
   </sheetData>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1001797.36</v>
+        <v>1004898.62</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2325487.01</v>
@@ -9816,16 +9816,16 @@
         <v>1001216.32</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>3.643</v>
+        <v>3.632</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.999</v>
+        <v>0.996</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>364.32</v>
+        <v>363.2</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>182.16</v>
+        <v>181.6</v>
       </c>
       <c r="K4" s="26" t="n">
         <v>19</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>542703.29</v>
+        <v>578256.1</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>97052.74000000001</v>
@@ -9853,16 +9853,16 @@
         <v>11505.46</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>0.336</v>
+        <v>0.316</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>33.65</v>
+        <v>31.58</v>
       </c>
       <c r="J5" s="27" t="n">
-        <v>16.82</v>
+        <v>15.79</v>
       </c>
       <c r="K5" s="28" t="n">
         <v>1</v>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>459094.08</v>
+        <v>426642.52</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2228434.27</v>
@@ -9890,16 +9890,16 @@
         <v>989710.86</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>7.552</v>
+        <v>8.127000000000001</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2.156</v>
+        <v>2.32</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>755.22</v>
+        <v>812.66</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>377.61</v>
+        <v>406.33</v>
       </c>
       <c r="K6" s="26" t="n">
         <v>18</v>
@@ -9989,7 +9989,7 @@
         <v>370955.58</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>37.03</v>
+        <v>36.91</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>10.16</v>
@@ -10011,7 +10011,7 @@
         <v>335261.08</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>33.47</v>
+        <v>33.36</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>9.19</v>
@@ -10029,11 +10029,11 @@
       <c r="B8" s="4" t="n">
         <v>324143.88</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>-324143.88</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>32.36</v>
+        <v>32.26</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>8.880000000000001</v>
@@ -10055,7 +10055,7 @@
         <v>273357.44</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>27.29</v>
+        <v>27.2</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>7.49</v>
@@ -10077,7 +10077,7 @@
         <v>262636.36</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>26.22</v>
+        <v>26.14</v>
       </c>
       <c r="E10" s="23" t="n">
         <v>7.2</v>
@@ -10099,7 +10099,7 @@
         <v>221305.92</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>22.09</v>
+        <v>22.02</v>
       </c>
       <c r="E11" s="21" t="n">
         <v>6.06</v>
@@ -10121,7 +10121,7 @@
         <v>211464.36</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>21.11</v>
+        <v>21.04</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>5.79</v>
@@ -10143,7 +10143,7 @@
         <v>168534.12</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>16.82</v>
+        <v>16.77</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>4.62</v>
@@ -10165,7 +10165,7 @@
         <v>165480.42</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>16.52</v>
+        <v>16.47</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>4.53</v>
@@ -10183,11 +10183,11 @@
       <c r="B15" s="13" t="n">
         <v>135933.6</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="18" t="n">
         <v>-135933.6</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>13.57</v>
+        <v>13.53</v>
       </c>
       <c r="E15" s="21" t="n">
         <v>3.72</v>
@@ -10258,13 +10258,13 @@
       <c r="B21" s="13" t="n">
         <v>428116.78</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="13" t="n">
         <v>428116.78</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>11.73</v>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       <c r="C22" s="4" t="n">
         <v>522258.94</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="19" t="n">
         <v>-425206.2</v>
       </c>
       <c r="E22" s="7" t="n">
@@ -10302,7 +10302,7 @@
       <c r="D23" s="13" t="n">
         <v>371626.8</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>10.18</v>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       <c r="C24" s="4" t="n">
         <v>324143.88</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="19" t="n">
         <v>-324143.88</v>
       </c>
       <c r="E24" s="7" t="n">
@@ -10340,7 +10340,7 @@
       <c r="D25" s="13" t="n">
         <v>267364.9</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>7.33</v>
       </c>
     </row>
@@ -10356,7 +10356,7 @@
       <c r="C26" s="4" t="n">
         <v>186748.67</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <v>-186748.67</v>
       </c>
       <c r="E26" s="7" t="n">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2.672</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="4">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>3.73</v>
+        <v>3.718</v>
       </c>
     </row>
     <row r="5">
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>98.79000000000001</v>
+        <v>98.48999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
@@ -734,7 +734,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-01  ·  Generated 2026-06-10T09:47:02  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-01  ·  Generated 2026-06-24T18:49:50  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
     </row>
     <row r="5">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3.632</v>
+        <v>5.526</v>
       </c>
     </row>
     <row r="6">
@@ -764,8 +764,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>0.996</v>
+      <c r="B6" s="5" t="n">
+        <v>2.89</v>
       </c>
     </row>
     <row r="7">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2.664</v>
+        <v>7.123</v>
       </c>
     </row>
     <row r="8">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>44873.5</v>
+        <v>117196.95</v>
       </c>
     </row>
     <row r="9">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>4.47</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="10">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>43.09</v>
+        <v>112.56</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.252</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="12">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.8213</v>
+        <v>0.8209</v>
       </c>
     </row>
     <row r="13">
@@ -846,7 +846,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>6.74 / 3.37</t>
+          <t>6.72 / 3.36</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>3.632</v>
+        <v>5.526</v>
       </c>
     </row>
     <row r="16">
@@ -868,7 +868,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>MS (36.91% NAV)</t>
+          <t>KLAC (210.45% NAV)</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>23.84</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="18">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>44873.5</v>
+        <v>117196.95</v>
       </c>
     </row>
     <row r="4">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>63450.31</v>
+        <v>165714.35</v>
       </c>
     </row>
     <row r="5">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>433036.27</v>
+        <v>1130968.93</v>
       </c>
     </row>
     <row r="6">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>43.09</v>
+        <v>112.56</v>
       </c>
     </row>
     <row r="7">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>37348.6</v>
+        <v>95957.89</v>
       </c>
     </row>
     <row r="8">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>43745.98</v>
+        <v>115645.66</v>
       </c>
     </row>
     <row r="10">
@@ -1030,131 +1030,131 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>MS/AWK</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>10307.82</v>
+        <v>53132.94</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>22.97</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>5858.42</v>
+        <v>32641.93</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>13.06</v>
+        <v>27.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>MS/AWK</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>4589.39</v>
+        <v>8063.49</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>10.23</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>3838.46</v>
+        <v>5775</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>8.550000000000001</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>3067.05</v>
+        <v>4939.71</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>6.83</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>2481.21</v>
+        <v>2029.07</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>5.53</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>CI/MTD</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1936.6</v>
+        <v>1776.67</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>4.32</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1931.05</v>
+        <v>1547.72</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1922.89</v>
+        <v>1513.96</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>4.29</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1813.36</v>
+        <v>1422.88</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>4.04</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="22">
@@ -1164,62 +1164,62 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1652</v>
+        <v>1154.13</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>3.68</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CI/MTD</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1450.71</v>
+        <v>1031.91</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>3.23</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1148.07</v>
+        <v>896.4299999999999</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>2.56</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1025.02</v>
+        <v>769.09</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>2.28</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>ORCL/LOW</t>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>889.2</v>
+        <v>471.02</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1.98</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -1466,8 +1466,8 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>67</v>
+      <c r="C14" s="4" t="n">
+        <v>670</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>1010394</v>
@@ -1550,8 +1550,8 @@
           <t>KLAC/LOW</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>42</v>
+      <c r="C18" s="4" t="n">
+        <v>420</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>1010394</v>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-133852.5</v>
+        <v>-357862.16</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>-13.32</v>
+        <v>-35.62</v>
       </c>
     </row>
     <row r="5">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-267704.99</v>
+        <v>-715724.3199999999</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>-26.64</v>
+        <v>-71.23</v>
       </c>
     </row>
     <row r="6">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-133852.5</v>
+        <v>-357862.16</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>-13.32</v>
+        <v>-35.62</v>
       </c>
     </row>
     <row r="7">
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-87020.66</v>
+        <v>-277338.58</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>-8.66</v>
+        <v>-27.6</v>
       </c>
     </row>
   </sheetData>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="C6" s="34" t="n">
-        <v>8.130000000000001</v>
+        <v>12.56</v>
       </c>
       <c r="D6" s="34" t="n">
         <v>3</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="C7" s="34" t="n">
-        <v>2.32</v>
+        <v>6.76</v>
       </c>
       <c r="D7" s="34" t="n">
         <v>0.5</v>
@@ -1876,11 +1876,11 @@
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C8" s="34" t="n">
-        <v>36.91</v>
+        <v>210.45</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>15</v>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C9" s="34" t="n">
-        <v>33.36</v>
+        <v>36.92</v>
       </c>
       <c r="D9" s="34" t="n">
         <v>15</v>
@@ -1928,11 +1928,11 @@
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>32.26</v>
+        <v>33.37</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>15</v>
@@ -1947,54 +1947,54 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
-        <v>23.84</v>
-      </c>
-      <c r="D11" s="32" t="n">
+      <c r="C11" s="36" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="D11" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>max_pair</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="D12" s="32" t="n">
+      <c r="C12" s="36" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="D12" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="32" t="n">
+      <c r="E12" s="36" t="n">
         <v>35</v>
       </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>2.66</v>
+        <v>7.12</v>
       </c>
       <c r="D13" s="34" t="n">
         <v>0.3</v>
@@ -2025,28 +2025,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>var_95_1d</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C14" s="36" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="D14" s="36" t="n">
+      <c r="C14" s="34" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="D14" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="36" t="n">
+      <c r="E14" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="36" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="E12" s="28" t="n">
-        <v>67</v>
+        <v>670</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>1940.04</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>129982.68</v>
+        <v>1299826.8</v>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
@@ -2736,13 +2736,13 @@
         </is>
       </c>
       <c r="E16" s="28" t="n">
-        <v>42</v>
+        <v>420</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>1940.04</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>81481.67999999999</v>
+        <v>814816.8</v>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
@@ -4063,11 +4063,11 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
-        <v>-3999.37</v>
+      <c r="C8" s="13" t="n">
+        <v>1165844.75</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>143797.86</v>
+        <v>1313641.98</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>0</v>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>4425.26</v>
+        <v>737760.38</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>160823.08</v>
+        <v>894158.2</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>0</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>14.9</v>
+        <v>15.24</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-0.6</v>
+        <v>-0.44</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>-15.5</v>
+        <v>-15.68</v>
       </c>
     </row>
     <row r="7">
@@ -4729,16 +4729,16 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>10.99</v>
+        <v>11.29</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>3.19</v>
+        <v>4.44</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>-7.8</v>
+        <v>-6.85</v>
       </c>
     </row>
     <row r="8">
@@ -4748,16 +4748,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24.67</v>
+        <v>25.27</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.74</v>
+        <v>4.76</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-20.93</v>
+        <v>-20.51</v>
       </c>
     </row>
     <row r="9">
@@ -4767,16 +4767,16 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>49.44</v>
+        <v>48.2</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>93.67</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>44.23</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="11">
@@ -4801,101 +4801,101 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>MS/AWK</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>22.97</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>13.06</v>
+        <v>27.85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>MS/AWK</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>10.23</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>8.550000000000001</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>6.83</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>5.53</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>CI/MTD</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>4.32</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>4.29</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>4.04</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="23">
@@ -4905,47 +4905,47 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>3.68</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CI/MTD</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>3.23</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>2.56</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>2.28</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>ORCL/LOW</t>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>1.98</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2.6</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.111 (t=-0.62)</t>
+          <t>-0.11 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>48.07</v>
+        <v>47.74</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>0.059</v>
@@ -5118,27 +5118,27 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>0.056 (t=0.39)</t>
+          <t>0.059 (t=0.41)</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>-0.116 (t=-0.52)</t>
+          <t>-0.119 (t=-0.54)</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>-0.06 (t=-0.31)</t>
+          <t>-0.059 (t=-0.3)</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>0.241 (t=1.31)</t>
+          <t>0.244 (t=1.32)</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>-0.207 (t=-0.72)</t>
+          <t>-0.208 (t=-0.72)</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>28.62</v>
+        <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1.03</v>
@@ -5167,32 +5167,32 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.069 (t=-0.42)</t>
+          <t>-0.073 (t=-0.44)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>-0.004 (t=-0.02)</t>
+          <t>0.001 (t=0.0)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.235 (t=1.04)</t>
+          <t>0.234 (t=1.03)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.103 (t=-0.49)</t>
+          <t>-0.106 (t=-0.5)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.022 (t=0.07)</t>
+          <t>0.023 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.065 (t=-0.55)</t>
+          <t>-0.064 (t=-0.53)</t>
         </is>
       </c>
     </row>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>-0.523</v>
+        <v>-0.525</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>3.81</v>
+        <v>3.836</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -5293,10 +5293,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1.259</v>
+        <v>1.26</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1.313</v>
+        <v>1.314</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0.054</v>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>-0.416</v>
+        <v>-0.454</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>2.244</v>
+        <v>2.375</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>1.605</v>
+        <v>1.613</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>1.677</v>
+        <v>1.693</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="6">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>0.165</v>
+        <v>0.24</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>12.035</v>
+        <v>12.251</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -5349,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2.513</v>
+        <v>2.526</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>2.513</v>
+        <v>2.526</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -5417,13 +5417,13 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.252</v>
+        <v>1.25</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.8213</v>
+        <v>0.8209</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>8.609999999999999</v>
@@ -5435,13 +5435,13 @@
         <v>77.2</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>6.74</v>
+        <v>6.72</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.632</v>
+        <v>5.526</v>
       </c>
     </row>
     <row r="10">
@@ -5451,13 +5451,13 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>1.437</v>
+        <v>1.413</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.8551</v>
+        <v>0.8506</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>8.65</v>
@@ -5469,10 +5469,10 @@
         <v>75.90000000000001</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>6.91</v>
+        <v>6.74</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>0.316</v>
@@ -5485,13 +5485,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0.368</v>
+        <v>0.383</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.6092</v>
+        <v>0.6137</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5035</v>
+        <v>4639</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.04</v>
@@ -5503,13 +5503,13 @@
         <v>80.7</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>8.127000000000001</v>
+        <v>12.559</v>
       </c>
     </row>
   </sheetData>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>155329.01</v>
+        <v>155150.5</v>
       </c>
     </row>
     <row r="6">
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2325487.01</v>
+        <v>4228666.25</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1534422.46</v>
+        <v>3425427.49</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1877143.41</v>
@@ -5641,16 +5641,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>3676243.11</v>
+        <v>5579422.35</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>2503433.82</v>
+        <v>4394438.85</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>3443683.26</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>2120433.21</v>
+        <v>2120254.7</v>
       </c>
     </row>
     <row r="9">
@@ -5679,13 +5679,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1347073.8</v>
+        <v>3250344.25</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>564075.33</v>
+        <v>2455194.43</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>910972.4300000001</v>
+        <v>911068.84</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -5698,13 +5698,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2671344.49</v>
+        <v>4574614.94</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1514086.47</v>
+        <v>3405205.57</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2446795.81</v>
+        <v>2446892.22</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>1067096.39</v>
@@ -5717,16 +5717,16 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1053336.82</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="13">
@@ -5736,16 +5736,16 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>3.632</v>
+        <v>5.526</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>2.511</v>
+        <v>4.423</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>3.424</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1.845</v>
+        <v>1.846</v>
       </c>
     </row>
     <row r="14">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.996</v>
+        <v>2.89</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.591</v>
+        <v>2.502</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>0.342</v>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>729951.54</v>
+        <v>1110587.39</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>496886.72</v>
+        <v>875087.73</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>682593.36</v>
@@ -5792,17 +5792,17 @@
           <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
-        <v>274947.08</v>
+      <c r="B16" s="18" t="n">
+        <v>-105779.98</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>492460.63</v>
+        <v>114145.55</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>314294.09</v>
+        <v>314197.68</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>664584.37</v>
+        <v>664405.86</v>
       </c>
     </row>
     <row r="17">
@@ -5815,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
@@ -5865,13 +5865,13 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>876665.88</v>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2325487.01</v>
+        <v>4228666.25</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1534422.46</v>
+        <v>3425427.49</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>1877143.41</v>
@@ -5922,13 +5922,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1320588.39</v>
+        <v>3223858.84</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>545075.11</v>
+        <v>2436194.21</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>880255.96</v>
+        <v>880352.37</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>876665.88</v>
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>155329.01</v>
+        <v>155150.5</v>
       </c>
     </row>
     <row r="33">
@@ -6093,16 +6093,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1053336.82</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="34">
@@ -6165,16 +6165,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>479492.41</v>
+        <v>478446.74</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>420303.88</v>
+        <v>419263.54</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>249710.29</v>
+        <v>248670.31</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>426377.54</v>
+        <v>425244.41</v>
       </c>
     </row>
     <row r="40">
@@ -6222,16 +6222,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>663803.38</v>
+        <v>662757.71</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>724040.99</v>
+        <v>723000.65</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>980263.26</v>
+        <v>979223.28</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>823644.49</v>
+        <v>822511.36</v>
       </c>
     </row>
     <row r="43">
@@ -6298,16 +6298,16 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>575306.51</v>
+        <v>574266.17</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>575110.5699999999</v>
+        <v>574070.59</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>626622.02</v>
+        <v>625488.89</v>
       </c>
     </row>
     <row r="47">
@@ -6320,13 +6320,13 @@
         <v>0.316</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.523</v>
+        <v>0.524</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1.256</v>
+        <v>1.258</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.628</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="48">
@@ -6374,16 +6374,16 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>541736.1</v>
+        <v>540690.4300000001</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>515154.03</v>
+        <v>514113.69</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>430620.59</v>
+        <v>429580.61</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>547956.72</v>
+        <v>546823.59</v>
       </c>
     </row>
     <row r="51">
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="53">
@@ -6655,16 +6655,16 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>479492.41</v>
+        <v>478446.74</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>420303.88</v>
+        <v>419263.54</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>249710.29</v>
+        <v>248670.31</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>426377.54</v>
+        <v>425244.41</v>
       </c>
     </row>
     <row r="67">
@@ -6674,16 +6674,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>575306.51</v>
+        <v>574266.17</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>575110.5699999999</v>
+        <v>574070.59</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>626622.02</v>
+        <v>625488.89</v>
       </c>
     </row>
     <row r="68">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>2228434.27</v>
+        <v>4131613.51</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1382394.52</v>
+        <v>3273399.55</v>
       </c>
       <c r="D75" s="4" t="n">
         <v>1559846.18</v>
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>3491932.15</v>
+        <v>5395111.39</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>2199696.71</v>
+        <v>4090701.74</v>
       </c>
       <c r="D76" s="13" t="n">
         <v>2713130.28</v>
@@ -6841,16 +6841,16 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>1826566.22</v>
+        <v>3728791</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>984379.21</v>
+        <v>2874457.97</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>1160682.71</v>
+        <v>1159739.14</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>271048.54</v>
+        <v>270093.92</v>
       </c>
     </row>
     <row r="79">
@@ -6860,16 +6860,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>3065289.63</v>
+        <v>4967514.41</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1785655.87</v>
+        <v>3675734.63</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2291353.4</v>
+        <v>2290409.83</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1141122.45</v>
+        <v>1140167.83</v>
       </c>
     </row>
     <row r="80">
@@ -6879,16 +6879,16 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>421776.88</v>
+        <v>422720.45</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>426714.8</v>
+        <v>427669.42</v>
       </c>
     </row>
     <row r="81">
@@ -6898,16 +6898,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>8.127000000000001</v>
+        <v>12.559</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>5.274</v>
+        <v>9.819000000000001</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>6.379</v>
+        <v>6.365</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>3.633</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="82">
@@ -6917,16 +6917,16 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>2.32</v>
+        <v>6.765</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>1.404</v>
+        <v>5.957</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>1.018</v>
+        <v>1.015</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.445</v>
+        <v>-0.444</v>
       </c>
     </row>
     <row r="83">
@@ -6936,10 +6936,10 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>693431.54</v>
+        <v>1074067.38</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>436734.24</v>
+        <v>814935.24</v>
       </c>
       <c r="D83" s="4" t="n">
         <v>538103.37</v>
@@ -6955,16 +6955,16 @@
         </is>
       </c>
       <c r="B84" s="18" t="n">
-        <v>-266789.02</v>
+        <v>-646470.4</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>-22693.4</v>
+        <v>-399968.13</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-116326.49</v>
+        <v>-115382.92</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>116627.65</v>
+        <v>117582.27</v>
       </c>
     </row>
     <row r="85">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C85" s="7" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-0</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="87">
@@ -7027,16 +7027,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>421776.88</v>
+        <v>422720.45</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>426714.8</v>
+        <v>427669.42</v>
       </c>
     </row>
     <row r="90">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>2228434.27</v>
+        <v>4131613.51</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1382394.52</v>
+        <v>3273399.55</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>1559846.18</v>
@@ -7084,16 +7084,16 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>1801791.75</v>
+        <v>3704016.53</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>968353.6800000001</v>
+        <v>2858432.44</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>1138069.3</v>
+        <v>1137125.73</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>253647.06</v>
+        <v>252692.44</v>
       </c>
     </row>
     <row r="93">
@@ -7103,16 +7103,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>421776.88</v>
+        <v>422720.45</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>426714.8</v>
+        <v>427669.42</v>
       </c>
     </row>
     <row r="94">
@@ -7239,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D100" s="15" t="n">
         <v>0</v>
@@ -7255,16 +7255,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>421776.88</v>
+        <v>422720.45</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>426714.8</v>
+        <v>427669.42</v>
       </c>
     </row>
     <row r="102">
@@ -7358,16 +7358,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>15551.27</v>
+        <v>15574.13</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>8011.17</v>
+        <v>8016.37</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>-48438.2</v>
+        <v>-48350.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>83399.83</v>
+        <v>83308.62</v>
       </c>
     </row>
     <row r="6">
@@ -7377,16 +7377,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>184.53</v>
+        <v>445.25</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>922.65</v>
+        <v>2226.26</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>3875.14</v>
+        <v>9350.309999999999</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>26756.95</v>
+        <v>64561.63</v>
       </c>
     </row>
     <row r="7">
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>97984.31</v>
+        <v>2001163.55</v>
       </c>
     </row>
     <row r="9">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2949.59</v>
+        <v>2944.26</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3145.53</v>
+        <v>3139.84</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>-48365.92</v>
+        <v>-48278.46</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>68924.16</v>
+        <v>67878.49000000001</v>
       </c>
     </row>
     <row r="12">
@@ -7522,16 +7522,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>12601.68</v>
+        <v>12629.87</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4865.64</v>
+        <v>4876.53</v>
       </c>
       <c r="D17" s="20" t="n">
-        <v>-72.28</v>
+        <v>-72.44</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>14475.67</v>
+        <v>15430.13</v>
       </c>
     </row>
     <row r="18">
@@ -7541,16 +7541,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>250.21</v>
+        <v>510.79</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1251.07</v>
+        <v>2553.97</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>5254.51</v>
+        <v>10726.66</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>36281.11</v>
+        <v>74065.03</v>
       </c>
     </row>
     <row r="19">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>84728.47</v>
+        <v>1987907.71</v>
       </c>
     </row>
     <row r="21">
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1053336.82</v>
+        <v>1053158.31</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -7661,16 +7661,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>15551.27</v>
+        <v>15574.13</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>8011.17</v>
+        <v>8016.37</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>-48438.2</v>
+        <v>-48350.9</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>83399.83</v>
+        <v>83308.62</v>
       </c>
     </row>
     <row r="7">
@@ -7718,16 +7718,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
     </row>
     <row r="10">
@@ -7743,10 +7743,10 @@
         <v>0.8</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>-4.6</v>
+        <v>-4.59</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>9.050000000000001</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -7759,7 +7759,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>-2.68</v>
+        <v>-2.69</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>-6.07</v>
@@ -7809,13 +7809,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>575306.51</v>
+        <v>574266.17</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>575110.5699999999</v>
+        <v>574070.59</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>626622.02</v>
+        <v>625488.89</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -7828,16 +7828,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>2949.59</v>
+        <v>2944.26</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>3145.53</v>
+        <v>3139.84</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-48365.92</v>
+        <v>-48278.46</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>68924.16</v>
+        <v>67878.49000000001</v>
       </c>
     </row>
     <row r="17">
@@ -7885,16 +7885,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
     </row>
     <row r="20">
@@ -7913,7 +7913,7 @@
         <v>-7.72</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>13.53</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="21">
@@ -7976,13 +7976,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>421776.88</v>
+        <v>422720.45</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>426714.8</v>
+        <v>427669.42</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -7995,16 +7995,16 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>12601.68</v>
+        <v>12629.87</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>4865.64</v>
+        <v>4876.53</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>-72.28</v>
+        <v>-72.44</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>14475.67</v>
+        <v>15430.13</v>
       </c>
     </row>
     <row r="27">
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
     </row>
     <row r="30">
@@ -8080,7 +8080,7 @@
         <v>-0.02</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>3.51</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="31">
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>8011.17</v>
+        <v>8016.37</v>
       </c>
     </row>
     <row r="5">
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-659896.29</v>
+        <v>-2563075.53</v>
       </c>
     </row>
     <row r="6">
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>436101.37</v>
+        <v>2339275.41</v>
       </c>
     </row>
     <row r="7">
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1011218.51</v>
+        <v>1011202.12</v>
       </c>
     </row>
     <row r="97">
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1025407</v>
+        <v>1025356.19</v>
       </c>
     </row>
     <row r="98">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1026941.31</v>
+        <v>1026905.51</v>
       </c>
     </row>
     <row r="99">
@@ -9206,7 +9206,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015258.85</v>
+        <v>1015273.3</v>
       </c>
     </row>
     <row r="100">
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003003.03</v>
+        <v>1003025.8</v>
       </c>
     </row>
     <row r="101">
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1013068.4</v>
+        <v>1013098.34</v>
       </c>
     </row>
     <row r="102">
@@ -9236,7 +9236,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1026667.89</v>
+        <v>1026718.34</v>
       </c>
     </row>
     <row r="103">
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1053397.75</v>
+        <v>1053504.94</v>
       </c>
     </row>
     <row r="104">
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1050736.08</v>
+        <v>1050844.96</v>
       </c>
     </row>
     <row r="105">
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1049499.07</v>
+        <v>1049581.91</v>
       </c>
     </row>
     <row r="106">
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1049134.93</v>
+        <v>1049200.21</v>
       </c>
     </row>
     <row r="107">
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1042919.9</v>
+        <v>1042965.78</v>
       </c>
     </row>
     <row r="108">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1048685.92</v>
+        <v>1048734.43</v>
       </c>
     </row>
     <row r="109">
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1042773.4</v>
+        <v>1042822.5</v>
       </c>
     </row>
     <row r="110">
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1044235.83</v>
+        <v>1044292.9</v>
       </c>
     </row>
     <row r="111">
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1070354.14</v>
+        <v>1070408.83</v>
       </c>
     </row>
     <row r="112">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1061514.84</v>
+        <v>1061559.43</v>
       </c>
     </row>
     <row r="113">
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1074870.62</v>
+        <v>1074879.59</v>
       </c>
     </row>
     <row r="114">
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080512.52</v>
+        <v>1080503.54</v>
       </c>
     </row>
     <row r="115">
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1086924.48</v>
+        <v>1086894.67</v>
       </c>
     </row>
     <row r="116">
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1071780.32</v>
+        <v>1071796.37</v>
       </c>
     </row>
     <row r="117">
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065526.09</v>
+        <v>1065522.69</v>
       </c>
     </row>
     <row r="118">
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1080594.32</v>
+        <v>1080563.67</v>
       </c>
     </row>
     <row r="119">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1075591.99</v>
+        <v>1075540.76</v>
       </c>
     </row>
     <row r="120">
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1071013.67</v>
+        <v>1070952.2</v>
       </c>
     </row>
     <row r="121">
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1073689.47</v>
+        <v>1073612.17</v>
       </c>
     </row>
     <row r="122">
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1074236.64</v>
+        <v>1074160.56</v>
       </c>
     </row>
     <row r="123">
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1084547.15</v>
+        <v>1084460.75</v>
       </c>
     </row>
     <row r="124">
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1085528.37</v>
+        <v>1085444.17</v>
       </c>
     </row>
     <row r="125">
@@ -9466,7 +9466,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1092616.33</v>
+        <v>1092531.84</v>
       </c>
     </row>
     <row r="126">
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1092781.06</v>
+        <v>1092690.79</v>
       </c>
     </row>
     <row r="127">
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1053336.82</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="128">
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1049687.33</v>
+        <v>1049512.64</v>
       </c>
     </row>
     <row r="129">
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1044100.12</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="130">
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1032626.83</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="131">
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1039700.39</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="132">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1037551.62</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="133">
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1019311.74</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="134">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1014163.76</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="135">
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>999293.04</v>
+        <v>999221.6800000001</v>
       </c>
     </row>
     <row r="136">
@@ -9576,7 +9576,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1011409.78</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="137">
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1014540.8</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="138">
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1011881.11</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="139">
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>998415.39</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="140">
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1014351.76</v>
+        <v>1014291.81</v>
       </c>
     </row>
     <row r="141">
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1023498.77</v>
+        <v>1023430.49</v>
       </c>
     </row>
     <row r="142">
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1023696.66</v>
+        <v>1023647.26</v>
       </c>
     </row>
     <row r="143">
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
     </row>
     <row r="144">
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1016573.57</v>
+        <v>1016545.25</v>
       </c>
     </row>
     <row r="145">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
     </row>
     <row r="146">
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
     </row>
     <row r="147">
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
     </row>
     <row r="148">
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
     </row>
   </sheetData>
@@ -9801,31 +9801,31 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2325487.01</v>
+        <v>4228666.25</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>1324270.69</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3649757.7</v>
+        <v>5552936.94</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1001216.32</v>
+        <v>2904395.56</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>3.632</v>
+        <v>5.526</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.996</v>
+        <v>2.89</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>363.2</v>
+        <v>552.64</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>181.6</v>
+        <v>276.32</v>
       </c>
       <c r="K4" s="26" t="n">
         <v>19</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>578256.1</v>
+        <v>577210.4300000001</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>97052.74000000001</v>
@@ -9859,10 +9859,10 @@
         <v>0.02</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>31.58</v>
+        <v>31.63</v>
       </c>
       <c r="J5" s="27" t="n">
-        <v>15.79</v>
+        <v>15.82</v>
       </c>
       <c r="K5" s="28" t="n">
         <v>1</v>
@@ -9875,31 +9875,31 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>426642.52</v>
+        <v>427596.98</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2228434.27</v>
+        <v>4131613.51</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1238723.41</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3467157.68</v>
+        <v>5370336.92</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>989710.86</v>
+        <v>2892890.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>8.127000000000001</v>
+        <v>12.559</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2.32</v>
+        <v>6.765</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>812.66</v>
+        <v>1255.93</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>406.33</v>
+        <v>627.97</v>
       </c>
       <c r="K6" s="26" t="n">
         <v>18</v>
@@ -9940,7 +9940,7 @@
     <row r="3">
       <c r="A3" s="29" t="inlineStr">
         <is>
-          <t>HHI=0.0759  ·  effective N pairs=13.2  ·  max pair=19.05% of gross</t>
+          <t>HHI=0.1132  ·  effective N pairs=8.8  ·  max pair=23.66% of gross</t>
         </is>
       </c>
     </row>
@@ -9979,108 +9979,108 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>370955.58</v>
+        <v>2114643.6</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>370955.58</v>
+        <v>2114643.6</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>36.91</v>
+        <v>210.45</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>10.16</v>
+        <v>38.08</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>335261.08</v>
+        <v>370955.58</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>335261.08</v>
+        <v>370955.58</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>33.36</v>
+        <v>36.92</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>9.19</v>
+        <v>6.68</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>324143.88</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>-324143.88</v>
+        <v>335261.08</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>335261.08</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>32.26</v>
+        <v>33.37</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>8.880000000000001</v>
+        <v>6.04</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>273357.44</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>273357.44</v>
+        <v>324143.88</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>-324143.88</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>27.2</v>
+        <v>32.26</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>7.49</v>
+        <v>5.84</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>262636.36</v>
+        <v>273357.44</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>262636.36</v>
+        <v>273357.44</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>26.14</v>
+        <v>27.2</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>7.2</v>
+        <v>4.92</v>
       </c>
       <c r="F10" s="26" t="n">
         <v>2</v>
@@ -10089,20 +10089,20 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>221305.92</v>
+        <v>262636.36</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>221305.92</v>
+        <v>262636.36</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>22.02</v>
+        <v>26.14</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>6.06</v>
+        <v>4.73</v>
       </c>
       <c r="F11" s="28" t="n">
         <v>2</v>
@@ -10111,20 +10111,20 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>211464.36</v>
+        <v>221305.92</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>211464.36</v>
+        <v>221305.92</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>21.04</v>
+        <v>22.02</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>5.79</v>
+        <v>3.99</v>
       </c>
       <c r="F12" s="26" t="n">
         <v>2</v>
@@ -10146,7 +10146,7 @@
         <v>16.77</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>4.62</v>
+        <v>3.04</v>
       </c>
       <c r="F13" s="28" t="n">
         <v>1</v>
@@ -10168,7 +10168,7 @@
         <v>16.47</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>4.53</v>
+        <v>2.98</v>
       </c>
       <c r="F14" s="26" t="n">
         <v>2</v>
@@ -10190,7 +10190,7 @@
         <v>13.53</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>3.72</v>
+        <v>2.45</v>
       </c>
       <c r="F15" s="28" t="n">
         <v>2</v>
@@ -10237,16 +10237,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1004974.13</v>
+        <v>2908153.37</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>134767.54</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>870206.59</v>
+        <v>2773385.83</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>23.84</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="21">
@@ -10265,7 +10265,7 @@
         <v>428116.78</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>11.73</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="22">
@@ -10284,7 +10284,7 @@
         <v>-425206.2</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-11.65</v>
+        <v>-7.66</v>
       </c>
     </row>
     <row r="23">
@@ -10303,7 +10303,7 @@
         <v>371626.8</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>10.18</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="24">
@@ -10322,7 +10322,7 @@
         <v>-324143.88</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-8.880000000000001</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="25">
@@ -10341,7 +10341,7 @@
         <v>267364.9</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>7.33</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="26">
@@ -10360,7 +10360,7 @@
         <v>-186748.67</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>-5.12</v>
+        <v>-3.36</v>
       </c>
     </row>
   </sheetData>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2.664</v>
+        <v>7.123</v>
       </c>
     </row>
     <row r="4">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>3.718</v>
+        <v>8.177</v>
       </c>
     </row>
     <row r="5">
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>98.48999999999999</v>
+        <v>287.9</v>
       </c>
     </row>
     <row r="6">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>23.84</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="11">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="B11" s="21" t="n">
-        <v>11.73</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="12">
@@ -10479,7 +10479,7 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>-11.65</v>
+        <v>-7.66</v>
       </c>
     </row>
     <row r="13">
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B13" s="21" t="n">
-        <v>10.18</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="14">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>-8.880000000000001</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="15">
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="B15" s="21" t="n">
-        <v>7.33</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="16">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>-5.12</v>
+        <v>-3.36</v>
       </c>
     </row>
   </sheetData>

--- a/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
@@ -734,7 +734,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-01  ·  Generated 2026-06-24T18:49:50  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-01  ·  Generated 2026-06-25T01:17:30  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
@@ -734,7 +734,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-01  ·  Generated 2026-06-25T01:17:30  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-01  ·  Generated 2026-06-25T01:34:59  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260602_153038.xlsx
@@ -734,7 +734,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-01  ·  Generated 2026-06-25T01:34:59  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-01  ·  Generated 2026-06-25T01:48:24  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>5.526</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="6">
@@ -764,8 +764,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>2.89</v>
+      <c r="B6" s="6" t="n">
+        <v>0.996</v>
       </c>
     </row>
     <row r="7">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7.123</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="8">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>117196.95</v>
+        <v>44873.5</v>
       </c>
     </row>
     <row r="9">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>11.66</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="10">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>112.56</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="11">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>5.526</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="16">
@@ -868,7 +868,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>KLAC (210.45% NAV)</t>
+          <t>MS (36.92% NAV)</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>49.94</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="18">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>117196.95</v>
+        <v>44873.5</v>
       </c>
     </row>
     <row r="4">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>165714.35</v>
+        <v>63450.31</v>
       </c>
     </row>
     <row r="5">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1130968.93</v>
+        <v>433036.27</v>
       </c>
     </row>
     <row r="6">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>112.56</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="7">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>95957.89</v>
+        <v>37348.6</v>
       </c>
     </row>
     <row r="8">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>115645.66</v>
+        <v>43745.98</v>
       </c>
     </row>
     <row r="10">
@@ -1030,131 +1030,131 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>MS/AWK</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>53132.94</v>
+        <v>10307.82</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>45.34</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>32641.93</v>
+        <v>5858.42</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>27.85</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>MS/AWK</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>8063.49</v>
+        <v>4589.39</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6.88</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>5775</v>
+        <v>3838.46</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>4.93</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>4939.71</v>
+        <v>3067.05</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>4.21</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>2029.07</v>
+        <v>2481.21</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>1.73</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>CI/MTD</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1776.67</v>
+        <v>1936.6</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1.52</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1547.72</v>
+        <v>1931.05</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1513.96</v>
+        <v>1922.89</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1.29</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1422.88</v>
+        <v>1813.36</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1.21</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="22">
@@ -1164,62 +1164,62 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1154.13</v>
+        <v>1652</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.98</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>CI/MTD</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1031.91</v>
+        <v>1450.71</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>0.88</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>896.4299999999999</v>
+        <v>1148.07</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>0.76</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>769.09</v>
+        <v>1025.02</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.66</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>ODFL/JKHY</t>
+          <t>ORCL/LOW</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>471.02</v>
+        <v>889.2</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>0.4</v>
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>
@@ -1470,7 +1470,7 @@
         <v>670</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1010394</v>
+        <v>10103938</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1554,7 +1554,7 @@
         <v>420</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1010394</v>
+        <v>10103938</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-357862.16</v>
+        <v>-133840.35</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>-35.62</v>
+        <v>-13.32</v>
       </c>
     </row>
     <row r="5">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-715724.3199999999</v>
+        <v>-267680.69</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>-71.23</v>
+        <v>-26.64</v>
       </c>
     </row>
     <row r="6">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-357862.16</v>
+        <v>-133840.35</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>-35.62</v>
+        <v>-13.32</v>
       </c>
     </row>
     <row r="7">
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-277338.58</v>
+        <v>-87020.66</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>-27.6</v>
+        <v>-8.66</v>
       </c>
     </row>
   </sheetData>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="C6" s="34" t="n">
-        <v>12.56</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D6" s="34" t="n">
         <v>3</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="C7" s="34" t="n">
-        <v>6.76</v>
+        <v>2.31</v>
       </c>
       <c r="D7" s="34" t="n">
         <v>0.5</v>
@@ -1876,11 +1876,11 @@
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C8" s="34" t="n">
-        <v>210.45</v>
+        <v>36.92</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>15</v>
@@ -1902,11 +1902,11 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C9" s="34" t="n">
-        <v>36.92</v>
+        <v>33.37</v>
       </c>
       <c r="D9" s="34" t="n">
         <v>15</v>
@@ -1928,11 +1928,11 @@
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>33.37</v>
+        <v>32.26</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>15</v>
@@ -1947,54 +1947,54 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="C11" s="36" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="D11" s="36" t="n">
+      <c r="C11" s="32" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="D11" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="36" t="n">
+      <c r="E11" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>max_pair</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C12" s="36" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="D12" s="36" t="n">
+      <c r="C12" s="32" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="D12" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="36" t="n">
+      <c r="E12" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>7.12</v>
+        <v>2.66</v>
       </c>
       <c r="D13" s="34" t="n">
         <v>0.3</v>
@@ -2025,28 +2025,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>var_95_1d</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C14" s="34" t="n">
-        <v>11.66</v>
-      </c>
-      <c r="D14" s="34" t="n">
+      <c r="C14" s="36" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="D14" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="F14" s="36" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
@@ -2563,10 +2563,10 @@
         <v>670</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1940.04</v>
+        <v>194</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1299826.8</v>
+        <v>129982.68</v>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         <v>420</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>1940.04</v>
+        <v>194</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>814816.8</v>
+        <v>81481.67999999999</v>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
@@ -4063,11 +4063,11 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
-        <v>1165844.75</v>
+      <c r="C8" s="18" t="n">
+        <v>-3999.37</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1313641.98</v>
+        <v>143797.86</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>0</v>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>737760.38</v>
+        <v>4425.26</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>894158.2</v>
+        <v>160823.08</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>0</v>
@@ -4801,101 +4801,101 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>MS/AWK</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>45.34</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>27.85</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>MS/AWK</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>6.88</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>4.93</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>4.21</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>1.73</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>CI/MTD</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>1.52</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>1.29</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>1.21</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="23">
@@ -4905,47 +4905,47 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.98</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>CI/MTD</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>0.88</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.76</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>0.66</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>ODFL/JKHY</t>
+          <t>ORCL/LOW</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.4</v>
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>
@@ -5441,7 +5441,7 @@
         <v>3.36</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>5.526</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="10">
@@ -5509,7 +5509,7 @@
         <v>0.37</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>12.559</v>
+        <v>8.108000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4228666.25</v>
+        <v>2325487.01</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3425427.49</v>
+        <v>1534422.46</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1877143.41</v>
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>5579422.35</v>
+        <v>3676243.11</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>4394438.85</v>
+        <v>2503433.82</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>3443683.26</v>
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>3250344.25</v>
+        <v>1347165.01</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>2455194.43</v>
+        <v>564189.4</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>911068.84</v>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4574614.94</v>
+        <v>2671435.7</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3405205.57</v>
+        <v>1514200.54</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>2446892.22</v>
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>5.526</v>
+        <v>3.632</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>4.423</v>
+        <v>2.511</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>3.424</v>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>2.89</v>
+        <v>0.996</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>2.502</v>
+        <v>0.591</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>0.342</v>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>1110587.39</v>
+        <v>729951.54</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>875087.73</v>
+        <v>496886.72</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>682593.36</v>
@@ -5792,11 +5792,11 @@
           <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
-        <v>-105779.98</v>
+      <c r="B16" s="13" t="n">
+        <v>274855.87</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>114145.55</v>
+        <v>492346.56</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>314197.68</v>
@@ -5815,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>4228666.25</v>
+        <v>2325487.01</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3425427.49</v>
+        <v>1534422.46</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>1877143.41</v>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>3223858.84</v>
+        <v>1320679.6</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>2436194.21</v>
+        <v>545189.1800000001</v>
       </c>
       <c r="D24" s="13" t="n">
         <v>880352.37</v>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>4131613.51</v>
+        <v>2228434.27</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>3273399.55</v>
+        <v>1382394.52</v>
       </c>
       <c r="D75" s="4" t="n">
         <v>1559846.18</v>
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>5395111.39</v>
+        <v>3491932.15</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>4090701.74</v>
+        <v>2199696.71</v>
       </c>
       <c r="D76" s="13" t="n">
         <v>2713130.28</v>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>3728791</v>
+        <v>1825611.76</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>2874457.97</v>
+        <v>983452.9399999999</v>
       </c>
       <c r="D78" s="13" t="n">
         <v>1159739.14</v>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>4967514.41</v>
+        <v>3064335.17</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>3675734.63</v>
+        <v>1784729.6</v>
       </c>
       <c r="D79" s="4" t="n">
         <v>2290409.83</v>
@@ -6898,10 +6898,10 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>12.559</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>9.819000000000001</v>
+        <v>5.262</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>6.365</v>
@@ -6917,10 +6917,10 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>6.765</v>
+        <v>2.315</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>5.957</v>
+        <v>1.4</v>
       </c>
       <c r="D82" s="17" t="n">
         <v>1.015</v>
@@ -6936,10 +6936,10 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>1074067.38</v>
+        <v>693431.54</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>814935.24</v>
+        <v>436734.24</v>
       </c>
       <c r="D83" s="4" t="n">
         <v>538103.37</v>
@@ -6955,10 +6955,10 @@
         </is>
       </c>
       <c r="B84" s="18" t="n">
-        <v>-646470.4</v>
+        <v>-265834.56</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>-399968.13</v>
+        <v>-21767.13</v>
       </c>
       <c r="D84" s="18" t="n">
         <v>-115382.92</v>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C85" s="7" t="n">
         <v>0</v>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>4131613.51</v>
+        <v>2228434.27</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>3273399.55</v>
+        <v>1382394.52</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>1559846.18</v>
@@ -7084,10 +7084,10 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>3704016.53</v>
+        <v>1800837.29</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>2858432.44</v>
+        <v>967427.41</v>
       </c>
       <c r="D92" s="13" t="n">
         <v>1137125.73</v>
@@ -7377,16 +7377,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>445.25</v>
+        <v>184.54</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>2226.26</v>
+        <v>922.72</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>9350.309999999999</v>
+        <v>3875.41</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>64561.63</v>
+        <v>26758.76</v>
       </c>
     </row>
     <row r="7">
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2001163.55</v>
+        <v>97984.31</v>
       </c>
     </row>
     <row r="9">
@@ -7541,16 +7541,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>510.79</v>
+        <v>250.08</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>2553.97</v>
+        <v>1250.42</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>10726.66</v>
+        <v>5251.76</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>74065.03</v>
+        <v>36262.15</v>
       </c>
     </row>
     <row r="19">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1987907.71</v>
+        <v>84728.47</v>
       </c>
     </row>
     <row r="21">
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-2563075.53</v>
+        <v>-659896.29</v>
       </c>
     </row>
     <row r="6">
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2339275.41</v>
+        <v>436096.17</v>
       </c>
     </row>
     <row r="7">
@@ -9804,28 +9804,28 @@
         <v>1004807.41</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4228666.25</v>
+        <v>2325487.01</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>1324270.69</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5552936.94</v>
+        <v>3649757.7</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2904395.56</v>
+        <v>1001216.32</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>5.526</v>
+        <v>3.632</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2.89</v>
+        <v>0.996</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>552.64</v>
+        <v>363.23</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>276.32</v>
+        <v>181.61</v>
       </c>
       <c r="K4" s="26" t="n">
         <v>19</v>
@@ -9878,28 +9878,28 @@
         <v>427596.98</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4131613.51</v>
+        <v>2228434.27</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1238723.41</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5370336.92</v>
+        <v>3467157.68</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2892890.1</v>
+        <v>989710.86</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>12.559</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>6.765</v>
+        <v>2.315</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1255.93</v>
+        <v>810.85</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>627.97</v>
+        <v>405.42</v>
       </c>
       <c r="K6" s="26" t="n">
         <v>18</v>
@@ -9940,7 +9940,7 @@
     <row r="3">
       <c r="A3" s="29" t="inlineStr">
         <is>
-          <t>HHI=0.1132  ·  effective N pairs=8.8  ·  max pair=23.66% of gross</t>
+          <t>HHI=0.0759  ·  effective N pairs=13.2  ·  max pair=19.05% of gross</t>
         </is>
       </c>
     </row>
@@ -9979,108 +9979,108 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2114643.6</v>
+        <v>370955.58</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2114643.6</v>
+        <v>370955.58</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>210.45</v>
+        <v>36.92</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>38.08</v>
+        <v>10.16</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>370955.58</v>
+        <v>335261.08</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>370955.58</v>
+        <v>335261.08</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>36.92</v>
+        <v>33.37</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>6.68</v>
+        <v>9.19</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>335261.08</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>335261.08</v>
+        <v>324143.88</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>-324143.88</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>33.37</v>
+        <v>32.26</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>6.04</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>324143.88</v>
-      </c>
-      <c r="C9" s="18" t="n">
-        <v>-324143.88</v>
+        <v>273357.44</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>273357.44</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>32.26</v>
+        <v>27.2</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>5.84</v>
+        <v>7.49</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>273357.44</v>
+        <v>262636.36</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>273357.44</v>
+        <v>262636.36</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>27.2</v>
+        <v>26.14</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>4.92</v>
+        <v>7.2</v>
       </c>
       <c r="F10" s="26" t="n">
         <v>2</v>
@@ -10089,20 +10089,20 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>262636.36</v>
+        <v>221305.92</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>262636.36</v>
+        <v>221305.92</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>26.14</v>
+        <v>22.02</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>4.73</v>
+        <v>6.06</v>
       </c>
       <c r="F11" s="28" t="n">
         <v>2</v>
@@ -10111,20 +10111,20 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>221305.92</v>
+        <v>211464.36</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>221305.92</v>
+        <v>211464.36</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>22.02</v>
+        <v>21.05</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>3.99</v>
+        <v>5.79</v>
       </c>
       <c r="F12" s="26" t="n">
         <v>2</v>
@@ -10146,7 +10146,7 @@
         <v>16.77</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>3.04</v>
+        <v>4.62</v>
       </c>
       <c r="F13" s="28" t="n">
         <v>1</v>
@@ -10168,7 +10168,7 @@
         <v>16.47</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>2.98</v>
+        <v>4.53</v>
       </c>
       <c r="F14" s="26" t="n">
         <v>2</v>
@@ -10190,7 +10190,7 @@
         <v>13.53</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="F15" s="28" t="n">
         <v>2</v>
@@ -10237,16 +10237,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2908153.37</v>
+        <v>1004974.13</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>134767.54</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2773385.83</v>
+        <v>870206.59</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>49.94</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="21">
@@ -10265,7 +10265,7 @@
         <v>428116.78</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>7.71</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="22">
@@ -10284,7 +10284,7 @@
         <v>-425206.2</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-7.66</v>
+        <v>-11.65</v>
       </c>
     </row>
     <row r="23">
@@ -10303,7 +10303,7 @@
         <v>371626.8</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.69</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="24">
@@ -10322,7 +10322,7 @@
         <v>-324143.88</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-5.84</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -10341,7 +10341,7 @@
         <v>267364.9</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>4.81</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="26">
@@ -10360,7 +10360,7 @@
         <v>-186748.67</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>-3.36</v>
+        <v>-5.12</v>
       </c>
     </row>
   </sheetData>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7.123</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="4">
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>8.177</v>
+        <v>3.719</v>
       </c>
     </row>
     <row r="5">
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>287.9</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="6">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>49.94</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="11">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="B11" s="21" t="n">
-        <v>7.71</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="12">
@@ -10479,7 +10479,7 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>-7.66</v>
+        <v>-11.65</v>
       </c>
     </row>
     <row r="13">
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B13" s="21" t="n">
-        <v>6.69</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="14">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>-5.84</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="B15" s="21" t="n">
-        <v>4.81</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="16">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>-3.36</v>
+        <v>-5.12</v>
       </c>
     </row>
   </sheetData>
